--- a/Instructor/data-solutions-UPDATED.xlsx
+++ b/Instructor/data-solutions-UPDATED.xlsx
@@ -757,10 +757,10 @@
     <t xml:space="preserve">AI is not a calculator - confirm math and totals against receipts.</t>
   </si>
   <si>
-    <t xml:space="preserve">=COPILOT("Based on this memo, flag any expense-policy concerns (missing itemized receipt, over a per-head meal limit, gift limit, unapproved/shadow-IT vendor, capitalization threshold). If none, return 'OK'.", C2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is judgment, not fact - treat as a prompt for a human reviewer.</t>
+    <t xml:space="preserve">=COPILOT("Using these limits: itemized receipt required over $25; meals up to $75 per person; gifts up to $100 per vendor; capitalize items of $2,500 or more; approved vendors only. Flag any expense-policy concerns in this memo. If none, return 'OK'.", C2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgment, not fact - treat as a prompt for a human reviewer. Note: the function is vanilla, so the limits must live in the prompt.</t>
   </si>
   <si>
     <t xml:space="preserve">=COPILOT("Rate the urgency implied by this memo as Normal, Medium, or High, and briefly why.", C2)</t>
@@ -3927,7 +3927,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>136</v>
       </c>

--- a/Instructor/data-solutions-UPDATED.xlsx
+++ b/Instructor/data-solutions-UPDATED.xlsx
@@ -15,6 +15,8 @@
     <sheet name="InvoiceRegister_Clean" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="ExpenseMemos_Extracted" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="COPILOT_Formulas" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RegionalSummary" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="QuarterlyTrend" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="271">
   <si>
     <t xml:space="preserve">AI in Excel for Finance &amp; Accounting Teams</t>
   </si>
@@ -70,6 +72,15 @@
     <t xml:space="preserve">Monthly actual vs. budget by cost center. Practice summarizing and variance review - and checking the AI's math against the grid.</t>
   </si>
   <si>
+    <t xml:space="preserve">RegionalSummary + QuarterlyTrend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus - customization demos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional sales data for the Copilot-chat before/after demos (custom instructions and the style-guide reference file).</t>
+  </si>
+  <si>
     <t xml:space="preserve">InvoiceRegister_Clean</t>
   </si>
   <si>
@@ -779,20 +790,72 @@
   </si>
   <si>
     <t xml:space="preserve">Note: COPILOT() requires a Microsoft 365 Copilot license and recalculates against a live model, so results can vary run to run. It is designed for text tasks - classify, extract, summarize - not precise calculation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YoY Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midwest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mountain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus dataset for the customization demos (Copilot chat, not the =COPILOT function).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue in $000s. For the style-guide chart demo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,6 +904,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF1F2120"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF1F2120"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -910,7 +981,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -953,6 +1024,22 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1207,7 +1294,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1269,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
@@ -1300,6 +1387,17 @@
       </c>
       <c r="C10" s="5" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1334,604 +1432,604 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>1250</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>980.5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1450</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>3300</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3300</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>212.75</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>8160.94</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-450</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1725</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1725</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>640</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>640</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>12750</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>2980.4</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>415.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1250</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>5400</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1965,39 +2063,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -2007,13 +2105,13 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -2023,13 +2121,13 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -2039,13 +2137,13 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2055,13 +2153,13 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -2071,13 +2169,13 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -2087,13 +2185,13 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -2103,13 +2201,13 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -2119,13 +2217,13 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2135,13 +2233,13 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2151,13 +2249,13 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2167,13 +2265,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2183,13 +2281,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2199,13 +2297,13 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2215,13 +2313,13 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -2231,7 +2329,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2262,30 +2360,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>106215</v>
@@ -2303,10 +2401,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>126355</v>
@@ -2324,10 +2422,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>101909</v>
@@ -2345,10 +2443,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>144689</v>
@@ -2366,10 +2464,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>87725</v>
@@ -2387,10 +2485,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>104124</v>
@@ -2408,10 +2506,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>127228</v>
@@ -2429,10 +2527,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>105147</v>
@@ -2450,10 +2548,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>153681</v>
@@ -2471,10 +2569,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>88818</v>
@@ -2492,10 +2590,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>112090</v>
@@ -2513,10 +2611,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>138792</v>
@@ -2534,10 +2632,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>111785</v>
@@ -2555,10 +2653,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>168697</v>
@@ -2576,10 +2674,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>96010</v>
@@ -2597,10 +2695,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>105559</v>
@@ -2618,10 +2716,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>129636</v>
@@ -2639,10 +2737,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>106452</v>
@@ -2660,10 +2758,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>147046</v>
@@ -2681,10 +2779,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>96251</v>
@@ -2702,10 +2800,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>107145</v>
@@ -2723,10 +2821,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>133492</v>
@@ -2744,10 +2842,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>101662</v>
@@ -2765,10 +2863,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>155638</v>
@@ -2786,10 +2884,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>93866</v>
@@ -2837,42 +2935,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>45296</v>
@@ -2884,27 +2982,27 @@
         <v>1250</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>45298</v>
@@ -2916,27 +3014,27 @@
         <v>980.5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>45301</v>
@@ -2948,27 +3046,27 @@
         <v>1450</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>45303</v>
@@ -2980,27 +3078,27 @@
         <v>3300</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>45309</v>
@@ -3012,27 +3110,27 @@
         <v>212.75</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>45313</v>
@@ -3042,27 +3140,27 @@
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>45323</v>
@@ -3074,27 +3172,27 @@
         <v>8160.94</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>45325</v>
@@ -3106,27 +3204,27 @@
         <v>-450</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>45327</v>
@@ -3138,27 +3236,27 @@
         <v>1725</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>45331</v>
@@ -3170,27 +3268,27 @@
         <v>640</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>45334</v>
@@ -3202,27 +3300,27 @@
         <v>640</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>45337</v>
@@ -3234,27 +3332,27 @@
         <v>12750</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>45340</v>
@@ -3266,27 +3364,27 @@
         <v>2980.4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>45342</v>
@@ -3298,27 +3396,27 @@
         <v>415.6</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>45344</v>
@@ -3330,27 +3428,27 @@
         <v>1250</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>45347</v>
@@ -3362,24 +3460,24 @@
         <v>5400</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -3425,423 +3523,423 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>182</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>47</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>9600</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>659.96</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>540</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>612</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>88</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>214.5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>35</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>1999.9</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>29</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>58</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -3880,89 +3978,376 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>4218500</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>3755000</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <f aca="false">(B2-C2)/C2</f>
+        <v>0.123435419440746</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>3860200</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>3980000</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <f aca="false">(B3-C3)/C3</f>
+        <v>-0.0301005025125628</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2974300</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2610000</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <f aca="false">(B4-C4)/C4</f>
+        <v>0.139578544061303</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2145900</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>2203000</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <f aca="false">(B5-C5)/C5</f>
+        <v>-0.0259192010894235</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>1487600</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <f aca="false">(B6-C6)/C6</f>
+        <v>0.229421487603306</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">SUM(B2:B6)</f>
+        <v>14686500</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <f aca="false">SUM(C2:C6)</f>
+        <v>13758000</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <f aca="false">(B7-C7)/C7</f>
+        <v>0.0674880069777584</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <f aca="false">SUM(E2:E6)</f>
+        <v>7687</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>980</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>930</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>945</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>960</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>690</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>720</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>760</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>560</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>540</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>520</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>320</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>352</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
